--- a/public/assets/GCP Workshop.xlsx
+++ b/public/assets/GCP Workshop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CF4116-B24C-4687-A8A7-E080ABE9CD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A40F68-FE1E-45DE-9FDF-A46E43A83EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="259">
   <si>
     <t>Timestamp</t>
   </si>
@@ -634,6 +634,174 @@
   </si>
   <si>
     <t>Ayushi Arora</t>
+  </si>
+  <si>
+    <t>mr.rajat08@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Rajat Mujalda</t>
+  </si>
+  <si>
+    <t>Dermatology Venereology and Leprosy</t>
+  </si>
+  <si>
+    <t>jnshreya6@gmail.com</t>
+  </si>
+  <si>
+    <t>Shreya jain</t>
+  </si>
+  <si>
+    <t>Jnshreya6@gmail.com</t>
+  </si>
+  <si>
+    <t>dr.vinaypatidar@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Vinay Patidar</t>
+  </si>
+  <si>
+    <t>Associate Professor</t>
+  </si>
+  <si>
+    <t>Practice of Medicine with Essentials of Pharmacology</t>
+  </si>
+  <si>
+    <t>shahanashah2@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Shahana Shah</t>
+  </si>
+  <si>
+    <t>Pathology and microbiology</t>
+  </si>
+  <si>
+    <t>mksshaikh91@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Shaikh M Khaliq</t>
+  </si>
+  <si>
+    <t>Professor and Head of Clinical Biochemistry, AIMS</t>
+  </si>
+  <si>
+    <t>Clinical Biochemistry</t>
+  </si>
+  <si>
+    <t>tinu.shehla@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Shehla Jaffri</t>
+  </si>
+  <si>
+    <t>Homeopathy</t>
+  </si>
+  <si>
+    <t>neha18ani@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Neha Jain</t>
+  </si>
+  <si>
+    <t>Dept. Of Homoeopathic Materia Medica( Homoeopathy)</t>
+  </si>
+  <si>
+    <t>jahanvisingh2312@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Jahanvi Singh</t>
+  </si>
+  <si>
+    <t>omkar3259@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Omkar Kale</t>
+  </si>
+  <si>
+    <t>Radiology</t>
+  </si>
+  <si>
+    <t>skdhakad55514@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Sevak verma</t>
+  </si>
+  <si>
+    <t>dr.rajesmangroliya@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Rajesh mangoliya</t>
+  </si>
+  <si>
+    <t>Homoeopathic (pathology)</t>
+  </si>
+  <si>
+    <t>schandel272@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr sunil chandel</t>
+  </si>
+  <si>
+    <t>Homoeopathy</t>
+  </si>
+  <si>
+    <t>geetavishnariya558@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Geeta vishnariya</t>
+  </si>
+  <si>
+    <t>Homoeopathy ,(FMT dept )</t>
+  </si>
+  <si>
+    <t>geetavishnariya@gmail.com</t>
+  </si>
+  <si>
+    <t>praveennarayanmishra@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Praveen Narayan Mishra</t>
+  </si>
+  <si>
+    <t>Homeopathic</t>
+  </si>
+  <si>
+    <t>drabhilashadutta@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Abhilasha Dutta</t>
+  </si>
+  <si>
+    <t>Prof and Head</t>
+  </si>
+  <si>
+    <t>Physiology</t>
+  </si>
+  <si>
+    <t>Drabhilashadutta@gmail.com</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>vidhitiwari61@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr vidhi Tiwari</t>
+  </si>
+  <si>
+    <t>assistant professor</t>
+  </si>
+  <si>
+    <t>physiotherapy</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -703,7 +871,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -833,10 +1001,55 @@
     </border>
     <border>
       <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF442F65"/>
       </left>
       <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
         <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
@@ -851,7 +1064,7 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
@@ -869,7 +1082,52 @@
         <color rgb="FF442F65"/>
       </right>
       <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="medium">
         <color rgb="FF442F65"/>
@@ -880,7 +1138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -930,19 +1188,46 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1225,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1278,41 +1563,41 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
+      <c r="A2" s="17">
         <v>46251.784363425926</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="20">
         <v>9300409555</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="6" t="s">
+      <c r="I2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="24"/>
+      <c r="K2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="L2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3283,41 +3568,673 @@
       </c>
     </row>
     <row r="53" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="17">
+      <c r="A53" s="11">
         <v>46263.573159722226</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F53" s="19">
+      <c r="F53" s="14">
         <v>9818783535</v>
       </c>
-      <c r="G53" s="18" t="s">
+      <c r="G53" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="H53" s="18" t="s">
+      <c r="H53" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I53" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="20"/>
-      <c r="K53" s="18" t="s">
+      <c r="I53" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="15"/>
+      <c r="K53" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L53" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="M53" s="21" t="s">
+      <c r="L53" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>46263.75439814815</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" s="8">
+        <v>9407133385</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="9"/>
+      <c r="K54" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11">
+        <v>46265.491701388892</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" s="14">
+        <v>7057726152</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="15"/>
+      <c r="K55" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L55" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="102.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
+        <v>46265.561712962961</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" s="8">
+        <v>9893537533</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="9"/>
+      <c r="K56" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11">
+        <v>46265.564618055556</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F57" s="14">
+        <v>7771944147</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="15"/>
+      <c r="K57" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
+        <v>46265.610995370371</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F58" s="8">
+        <v>9826647786</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J58" s="9"/>
+      <c r="K58" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
+        <v>46266.251701388886</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="F59" s="14">
+        <v>7987617445</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H59" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="15"/>
+      <c r="K59" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L59" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="90" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
+        <v>46266.347395833334</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60" s="8">
+        <v>9584826515</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="9"/>
+      <c r="K60" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11">
+        <v>46266.377800925926</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F61" s="14">
+        <v>7266935975</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
+        <v>46266.378067129626</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F62" s="8">
+        <v>9893450099</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="9"/>
+      <c r="K62" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
+        <v>46266.3828587963</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>7580938636</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="15"/>
+      <c r="K63" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
+        <v>46266.437118055554</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F64" s="8">
+        <v>93407769555</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="K64" s="9"/>
+      <c r="L64" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
+        <v>46266.437835648147</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F65" s="14">
+        <v>9131870636</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="H65" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="5">
+        <v>46266.438113425924</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F66" s="8">
+        <v>9826244142</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11">
+        <v>46266.439189814817</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="14">
+        <v>7379421274</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L67" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="21">
+        <v>46266.471678240741</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="F68" s="23">
+        <v>9981964722</v>
+      </c>
+      <c r="G68" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="I68" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="K68" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="M68" s="26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="27">
+        <v>46266.497858796298</v>
+      </c>
+      <c r="B69" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F69" s="29">
+        <v>8005685287</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="K69" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="L69" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69" s="30" t="s">
         <v>21</v>
       </c>
     </row>

--- a/public/assets/GCP Workshop.xlsx
+++ b/public/assets/GCP Workshop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A40F68-FE1E-45DE-9FDF-A46E43A83EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D6FF8C-CD1F-47FE-BFE5-3C553E77223B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="280">
   <si>
     <t>Timestamp</t>
   </si>
@@ -802,13 +802,76 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>drmankashakhan@gmail.com</t>
+  </si>
+  <si>
+    <t>Mankasha Khan</t>
+  </si>
+  <si>
+    <t>MBBS</t>
+  </si>
+  <si>
+    <t>Otorhinolaryngology</t>
+  </si>
+  <si>
+    <t>Mbbs intern</t>
+  </si>
+  <si>
+    <t>vyasmahi06@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahi Vyas</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t>ENT</t>
+  </si>
+  <si>
+    <t>amaltasreshmashekh@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Reshma shekh</t>
+  </si>
+  <si>
+    <t>Swasthavritta evam yoga (Ayurveda)</t>
+  </si>
+  <si>
+    <t>registrar@amaltasuniversity.in</t>
+  </si>
+  <si>
+    <t>Dr Abhay K. Gupta</t>
+  </si>
+  <si>
+    <t>Registrar, Director of academics, HOD of ENT</t>
+  </si>
+  <si>
+    <t>drprashantw@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Prashant Wadagbalkar</t>
+  </si>
+  <si>
+    <t>M S</t>
+  </si>
+  <si>
+    <t>AIMS</t>
+  </si>
+  <si>
+    <t>‪98262 47595‬</t>
+  </si>
+  <si>
+    <t>MS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -844,6 +907,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -871,7 +940,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1134,11 +1203,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1228,6 +1372,42 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1510,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -4238,6 +4418,183 @@
         <v>21</v>
       </c>
     </row>
+    <row r="70" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="31">
+        <v>46266.724826388891</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="E70" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="F70" s="33">
+        <v>7974275417</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="H70" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="I70" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="34"/>
+      <c r="K70" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L70" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11">
+        <v>46266.727777777778</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F71" s="14">
+        <v>9926841097</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="15"/>
+      <c r="K71" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
+        <v>46266.786469907405</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F72" s="8">
+        <v>9165424431</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="9"/>
+      <c r="K72" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
+        <v>46266.727777777778</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="F73" s="14">
+        <v>9205383081</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="36"/>
+    </row>
+    <row r="74" spans="1:13" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="37">
+        <v>46266.727777777778</v>
+      </c>
+      <c r="B74" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="D74" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="E74" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="G74" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="H74" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="I74" s="41"/>
+      <c r="J74" s="41"/>
+      <c r="K74" s="41"/>
+      <c r="L74" s="41"/>
+      <c r="M74" s="42"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
